--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131036071</v>
       </c>
       <c r="B3" t="n">
-        <v>97879</v>
+        <v>97880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131036071</v>
       </c>
       <c r="B3" t="n">
-        <v>97880</v>
+        <v>97883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>131036071</v>
       </c>
       <c r="B3" t="n">
-        <v>97883</v>
+        <v>97884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131036065</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131036071</v>
       </c>
       <c r="B3" t="n">
-        <v>97884</v>
+        <v>97886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131036065</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131036071</v>
       </c>
       <c r="B3" t="n">
-        <v>97886</v>
+        <v>97887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131036065</v>
+        <v>131036058</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327409</v>
+        <v>327350</v>
       </c>
       <c r="R2" t="n">
-        <v>6453623</v>
+        <v>6453625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,22 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131036071</v>
+        <v>131036065</v>
       </c>
       <c r="B3" t="n">
-        <v>97887</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327355</v>
+        <v>327409</v>
       </c>
       <c r="R3" t="n">
-        <v>6453737</v>
+        <v>6453623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,19 +859,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -881,11 +880,11 @@
         <v>131242796</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -980,6 +979,529 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131242840</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lille-Väktor, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>327428</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453550</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126339753</v>
+      </c>
+      <c r="B6" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lille-Väktor, dammen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>327460</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6453669</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127135559</v>
+      </c>
+      <c r="B7" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillevekotor, dammen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>327469</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6453631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131036071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjöbacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>327355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6453737</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131036079</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjöbacken, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>327414</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6453734</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23559-2023 artfynd.xlsx
+++ b/artfynd/A 23559-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131036058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131036065</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242796</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131242840</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339753</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127135559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131036071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,8 +1542,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131036079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>